--- a/AAII_Financials/Quarterly/T_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/T_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>T</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31558000</v>
+      </c>
+      <c r="E8" s="3">
         <v>31506000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33466000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30709000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30847000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30626000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32298000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30213000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29797000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30028000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32022000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30350000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29917000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30139000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31343000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30043000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29643000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29712000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31095000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31326000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35740000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35877000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>45691000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>42340000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>40950000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>42779000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>46821000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44588000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>44957000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>44827000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>47993000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>45739000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>38986000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>38038000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>41676000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>39668000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>39837000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>39365000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>41841000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>40890000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12047000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12566000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14818000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11819000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12150000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12033000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14195000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11630000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11442000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11954000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13911000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12054000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11827000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12331000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13571000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12201000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12341000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12735000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14225000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13433000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16158000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16591000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>22910000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19839000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17983000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19281000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>22736000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>20154000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>20512000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>20739000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23309000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>20706000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17458000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17946000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>21926000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>19169000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>18605000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>18110000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>21119000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>18890000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19511000</v>
+      </c>
+      <c r="E10" s="3">
         <v>18940000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18648000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18890000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18697000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18593000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18103000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18583000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18355000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18074000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18111000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18296000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18090000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17808000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17772000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17842000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17302000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16977000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16870000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17893000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19582000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19286000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22781000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22501000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22967000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23498000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24085000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24434000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24445000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24088000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24684000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>25033000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21528000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>20092000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>19750000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>20499000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>21232000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>21255000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>20722000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>22000000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,19 +1219,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>843000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1227,11 +1240,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>955000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1239,11 +1252,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>954000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,130 +1467,136 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>456000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5500000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>585000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>81000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4422000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>480000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>360000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>704000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>604000</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26753000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>123000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>646000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>93000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>130000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-24000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16344000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>73000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2315000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-911000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1425000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>45000</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2955000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>60000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>36000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>38000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>361000</v>
       </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1582,121 +1604,124 @@
         <v>4966000</v>
       </c>
       <c r="E15" s="3">
+        <v>4966000</v>
+      </c>
+      <c r="F15" s="3">
         <v>5128000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5317000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5251000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5190000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5374000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5087000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5072000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5047000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4766000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4705000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4675000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4631000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4595000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4514000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4450000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4462000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4500000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4457000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4429000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4466000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6979000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7030000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7285000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7222000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>6961000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>6949000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7101000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7206000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7892000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8166000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>6378000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>5994000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>6071000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>6042000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>6147000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>6127000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>6129000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>6579000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23736000</v>
+      </c>
+      <c r="E17" s="3">
         <v>24347000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27303000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24082000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23837000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23860000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26425000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23077000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22960000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23424000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26775000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23141000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22638000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23340000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52435000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24031000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24687000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24175000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26201000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25089000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28168000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28683000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>56436000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>36208000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37418000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>35293000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>41500000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>36687000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>37457000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>37594000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>41833000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>38470000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>32520000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>31837000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>40395000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>33861000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>33311000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>33009000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>37593000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>34482000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7822000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7159000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6163000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6627000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7010000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6766000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5873000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7136000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6837000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6604000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5247000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7209000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7279000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6799000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21092000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6012000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4956000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5537000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4894000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6237000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7572000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7194000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10745000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6132000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3532000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7486000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5321000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7901000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7500000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7233000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6160000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7269000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6466000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6201000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1281000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>5807000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6526000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6356000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4248000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>6408000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-169000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-80000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-349000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-226000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-743000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1468000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1177000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-391000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-433000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-349000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-119000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-37000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-494000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-583000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-545000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2662000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2806000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2678000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2873000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1705000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1188000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4224000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2914000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-226000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1007000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>797000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-932000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-278000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>279000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1697000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>989000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2337000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1711000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-638000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>853000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>939000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>315000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>164000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12957000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12205000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11640000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12170000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13004000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13424000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12424000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12614000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12342000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12000000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10132000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11951000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12448000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12013000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17042000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13188000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12212000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12677000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12267000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12399000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11846000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17227000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6680000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12936000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11824000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15505000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12148000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>13918000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>14323000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>14718000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15749000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>16424000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>15181000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>13906000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6714000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>12702000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>13612000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>12798000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>10541000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>12996000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1883000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1813000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1791000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1655000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1658000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1661000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1675000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1699000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1724000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1726000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1662000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1608000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1708000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1560000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1420000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1502000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1626000</v>
       </c>
       <c r="U22" s="3">
         <v>1626000</v>
       </c>
       <c r="V22" s="3">
+        <v>1626000</v>
+      </c>
+      <c r="W22" s="3">
         <v>1627000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1640000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1823000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1894000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1972000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2041000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2018000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2049000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2083000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2149000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2141000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2112000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2051000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2023000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1771000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1926000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1686000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1395000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1293000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1221000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1224000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5822000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5398000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4265000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10653000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6098000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5991000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5308000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1430000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5091000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4869000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2936000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4980000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6165000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5767000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23197000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7254000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6260000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6589000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6141000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6315000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7120000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9595000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15553000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3934000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2498000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6265000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3138000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4886000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5073000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5371000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5745000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6207000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6780000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6141000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1283000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4974000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6070000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5378000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3191000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>5193000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1179000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>109000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>976000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1237000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1299000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1285000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1118000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>354000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1154000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1403000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1314000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-77000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>908000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1509000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1440000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>939000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1296000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1151000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2009000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2038000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>766000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>935000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1302000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>434000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>937000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1099000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1023000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1333000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1391000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1532000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1382000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-148000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1851000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2056000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1804000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>676000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1775000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5038000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4219000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4156000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9677000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4861000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4692000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4408000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>145000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3949000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3751000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2582000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3826000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4762000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4453000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23120000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6346000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4751000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5149000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5202000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5019000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5969000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7586000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13515000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3168000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1563000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4963000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2704000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3949000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3974000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4348000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4412000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4816000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5248000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4759000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1135000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3123000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4014000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3574000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2515000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>3418000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4591000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3793000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3752000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9278000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4464000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4395000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4031000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-226000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3546000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3395000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2135000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3444000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4437000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4176000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23536000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5924000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4319000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4747000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4804000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4614000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5609000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7144000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13938000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2762000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1229000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4578000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2391000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3700000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3713000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4096000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4140000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4718000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4662000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1234000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>3029000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3915000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3469000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2437000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>3328000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,17 +3179,20 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-38000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -3167,37 +3227,37 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-35000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>53000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-214000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>15000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>188000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1254000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4095000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>356000</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3214,11 +3274,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>718000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3226,11 +3286,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>20271000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E32" s="3">
         <v>80000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>349000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>226000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>743000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1468000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1177000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>391000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>433000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>349000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>119000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>37000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>494000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>583000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>545000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2662000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2806000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2678000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2873000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1705000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1188000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4224000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2914000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>226000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1007000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-797000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>134000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>932000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>278000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-279000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1697000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-989000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2337000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1711000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>638000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-853000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-939000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-315000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-164000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3829000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3788000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9314000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4500000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4351000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4080000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-174000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3597000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3445000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2188000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3495000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4489000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4228000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23571000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5977000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4105000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4762000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4992000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5868000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1514000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7500000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13938000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2762000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1229000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4578000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2391000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3700000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3713000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4096000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4858000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4718000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4662000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>19037000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>3029000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3915000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3469000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>3328000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3829000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3788000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9314000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4500000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4351000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4080000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-174000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3597000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3445000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2188000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3495000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4489000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4228000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23571000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5977000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4105000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4762000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4992000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5868000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1514000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7500000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13938000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2762000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1229000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4578000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2391000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3700000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3713000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4096000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4858000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4718000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4662000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>19037000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>3029000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3915000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3469000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>3328000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17570000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11964000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18234000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20272000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10499000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6885000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3298000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2586000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3093000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3520000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6722000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7540000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9528000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2821000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3701000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2423000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4018000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38565000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40392000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21270000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11869000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11342000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9740000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9758000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16941000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9955000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12130000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6588000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8423000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6516000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5204000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8657000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13523000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>48872000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>50498000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>48499000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>25617000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>14884000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5788000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>5895000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4325,41 +4414,41 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>80000</v>
       </c>
-      <c r="G42" s="3">
-        <v>71000</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>94000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>61000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>62000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>66000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>94000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>74000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,195 +4524,201 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14552000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14392000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14312000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21014000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14067000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14341000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15389000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14423000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14986000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14653000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15134000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13783000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13763000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14667000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18153000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18125000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18126000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23960000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19061000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20390000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20052000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16971000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>23745000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>22646000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22356000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23191000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25816000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26022000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25375000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>26743000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29164000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>28670000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>27562000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>19538000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18303000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>17899000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>17229000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>17127000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>18400000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>18416000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2368000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2451000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2420000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2886000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2357000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2593000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2270000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2529000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1816000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2127000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2177000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2520000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2348000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2791000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3123000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3935000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3241000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3153000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3325000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3088000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2810000</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>8</v>
@@ -4640,8 +4735,8 @@
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
@@ -4679,618 +4774,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5303000</v>
+      </c>
+      <c r="E45" s="3">
         <v>5207000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5412000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5332000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5285000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5267000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>5340000</v>
       </c>
       <c r="J45" s="3">
         <v>5340000</v>
       </c>
       <c r="K45" s="3">
+        <v>5340000</v>
+      </c>
+      <c r="L45" s="3">
         <v>5389000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5461000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5573000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5521000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5479000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5421000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8131000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7812000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9100000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11178000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>129159000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12482000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>28138000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>34441000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>18523000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17567000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17258000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19558000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16815000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>18085000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>13420000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>13213000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>17059000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>15780000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>14201000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>10095000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>10345000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>9959000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>10701000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>13716000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>14181000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>13063000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51834000</v>
+      </c>
+      <c r="E46" s="3">
         <v>46282000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>48732000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54579000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39306000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33780000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31168000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29799000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29868000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30445000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36458000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35620000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36672000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29903000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33108000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32295000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>34485000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>76856000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>170768000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>57230000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>62869000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>62754000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>52008000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>49971000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>56555000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>52704000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>54761000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>50695000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47218000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>46472000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>51427000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>53107000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>55286000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>78505000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>79146000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>76357000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>53547000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>45727000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>38369000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>37374000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2814000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2717000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2715000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1637000</v>
       </c>
-      <c r="G47" s="3">
-        <v>1611000</v>
-      </c>
       <c r="H47" s="3">
+        <v>2609000</v>
+      </c>
+      <c r="I47" s="3">
         <v>1534000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1898000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1418000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1691000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2013000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1251000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2929000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3919000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3985000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3533000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3964000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4523000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5943000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6168000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8629000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1853000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1805000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1780000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2325000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2302000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3606000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3695000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4137000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4133000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6230000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6245000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6128000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8007000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2623000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1560000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1627000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1615000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1551000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1674000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1679000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>156996000</v>
+      </c>
+      <c r="E48" s="3">
         <v>155880000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>154201000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>152576000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>150588000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>149459000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>149780000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>148743000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>148354000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>148519000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>149394000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>149497000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>150364000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>150077000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>149259000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>148827000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>146943000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>151100000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>143473000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>148760000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>147981000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>149022000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>152029000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>153268000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>153637000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>152929000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>154167000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>155793000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>154724000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>152286000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>131473000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>130348000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>129556000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>125124000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>125222000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>126462000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>126184000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>125292000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>124899000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>123922000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>199051000</v>
+      </c>
+      <c r="E49" s="3">
         <v>199117000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>196827000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>196450000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>196230000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>196031000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>195722000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>195822000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>200410000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>200558000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>200356000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>200299000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>198242000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>197743000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>197341000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>221943000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>221674000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>292073000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>245841000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>292929000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>270475000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>272876000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>281575000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>297432000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>299327000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>300010000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>303858000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>303853000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>307421000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>309008000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>310197000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>312576000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>312052000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>219117000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>219725000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>221087000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>221804000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>221871000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>222067000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>223473000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9774000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9310000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10081000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10453000</v>
       </c>
-      <c r="G52" s="3">
-        <v>10278000</v>
-      </c>
       <c r="H52" s="3">
+        <v>9280000</v>
+      </c>
+      <c r="I52" s="3">
         <v>9170000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8761000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10464000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10083000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10151000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11681000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10428000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11276000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11070000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19612000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>19434000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18808000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>51223000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>38235000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>39559000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>61532000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>60528000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>38369000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>35557000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36077000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>36105000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>35188000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>34318000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>33418000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34388000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>32522000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>32711000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>29790000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>20974000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>18444000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>18332000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>17645000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>17462000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>16812000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>16527000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>428359000</v>
+      </c>
+      <c r="E54" s="3">
         <v>421188000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>420198000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>423213000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>405491000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>397467000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>394795000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>393719000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>398026000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>399428000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>407060000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>406698000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>408453000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>400873000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>402853000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>426463000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>426433000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>577195000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>551622000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>547107000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>544710000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>546985000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>525761000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>538553000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>547898000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>545354000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>551669000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>548796000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>546914000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>548384000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>531864000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>534870000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>534691000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>446343000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>444097000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>443865000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>420795000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>411903000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>403821000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>402975000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35911000</v>
+      </c>
+      <c r="E57" s="3">
         <v>35603000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29910000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35570000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31956000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31873000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27433000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27742000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27125000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23518000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27309000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>28913000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27196000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26144000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39097000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36642000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33193000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43151000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>35702000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>44177000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>44678000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>44681000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45495000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39245000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>38407000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37328000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>42357000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>40350000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>38647000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39074000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>42988000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>39145000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>35377000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>31475000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>34470000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>28928000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>26471000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>27120000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>31138000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>28849000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11198000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8292000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12032000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12286000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10447000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9980000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7407000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3480000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6132000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8275000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12482000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16932000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20960000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>25947000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7597000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6429000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6829000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>28380000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>25865000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>24935000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>24016000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19505000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3470000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5898000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15576000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17067000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11838000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11608000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12772000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11538000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10255000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14905000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>21672000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>29322000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>38374000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8551000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>10831000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>12681000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>9832000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>7982000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6273000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6526000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6840000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6020000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6162000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6146000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7427000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9436000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9172000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13041000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6820000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5839000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6003000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6059000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9479000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9186000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9167000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10963000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44663000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12489000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13432000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12422000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14473000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14422000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15486000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15309000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14716000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16168000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14957000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14040000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11177000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11370000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11544000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9783000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8545000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10214000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>10710000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10889000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9606000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>10271000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53382000</v>
+      </c>
+      <c r="E60" s="3">
         <v>50421000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53780000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53876000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48565000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47999000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46872000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40658000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>42429000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44834000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51127000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51684000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54159000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>58150000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56173000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52257000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>49189000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>82494000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>106230000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>81601000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>82126000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>76608000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>63438000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>59565000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>69469000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>69704000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>68911000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>68126000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>66376000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>64652000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>64420000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>65420000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>68593000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>70580000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>81389000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>47693000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>48012000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>50690000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>50576000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>47102000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>154558000</v>
+      </c>
+      <c r="E61" s="3">
         <v>151459000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>147528000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>147881000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>141542000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>135308000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>137049000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>144523000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>143473000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>143801000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>146799000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>145675000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>147733000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>143612000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>128423000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>123854000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>129747000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>180225000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>151011000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>155664000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>155767000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>160694000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>153775000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>152980000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>153388000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>147202000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>151309000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>153568000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>157790000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>163942000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>166250000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>168513000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>168495000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>133724000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>125972000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>154728000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>132824000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>120568000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>113681000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>117239000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23312000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24146000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23608000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24685000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23142000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24137000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22685000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23067000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23138000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22635000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22319000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24347000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23848000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26411000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>111800000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>110374000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>112190000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>127920000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>110526000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>128539000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>126971000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>126604000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>129308000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>130952000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>131588000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>132999000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>129515000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>132775000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>128667000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>124839000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>107310000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>115966000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>113473000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>94963000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>94729000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>115335000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>114101000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>115664000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>115454000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>114031000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>299920000</v>
+      </c>
+      <c r="E66" s="3">
         <v>293566000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>291706000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>294474000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>282114000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>275628000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>274570000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>275459000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>276702000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>278833000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>287645000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>286871000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>290408000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>292527000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>305353000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>304057000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>308687000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>408159000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>385290000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>383336000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>382414000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>381497000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>364088000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>363000000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>372002000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>367575000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>367448000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>365747000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>362657000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>363272000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>347775000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>351022000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>351711000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>300423000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>303236000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>318905000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>296070000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>288062000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>280686000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>279364000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20293000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17620000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15768000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13974000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6680000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4215000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1871000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-185000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1570000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5015000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7203000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10698000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15187000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19415000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6127000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2128000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45041000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>42350000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>41091000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38947000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41154000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37457000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>55094000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>56045000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>58534000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>57936000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>59347000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>59389000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>59424000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>58753000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>57624000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>56555000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>55067000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>50500000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>36074000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>36067000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>35175000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>34734000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>35319000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110444000</v>
+      </c>
+      <c r="E76" s="3">
         <v>109660000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>110533000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>110708000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>105272000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>103744000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>104372000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>102351000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>105310000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>104540000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>103297000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>103703000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101903000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>99396000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97500000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>122406000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>117746000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>169036000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>166332000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>163771000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>162296000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>165488000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>161673000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>175553000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>175896000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>177779000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>184221000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>183049000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>184257000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>185112000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>184089000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>183848000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>182980000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>145920000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>140861000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>124960000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>124725000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>123841000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>123135000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>123611000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3829000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3788000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9314000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4500000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4351000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4080000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-174000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3597000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3445000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2188000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3495000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4489000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4228000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23571000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5977000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4105000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4762000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4992000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5868000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1514000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7500000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13938000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2762000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1229000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4578000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2391000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3700000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3713000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4096000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4858000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4718000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4662000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>19037000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>3029000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3915000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3469000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>3328000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5251000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5190000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2182000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5074000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5057000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5032000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1614000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4684000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4658000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4614000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1514000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4498000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4433000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4435000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4595000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4514000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3373000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5539000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5673000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5619000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5761000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5809000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6979000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7030000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7285000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7222000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6961000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6949000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7101000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7206000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7892000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8166000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6378000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5994000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>6071000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6042000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>6147000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>6127000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>6129000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>6579000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10870000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7557000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11320000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10152000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9763000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9049000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11896000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10235000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9093000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7547000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11378000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10336000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9922000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6678000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10313000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10071000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5907000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5732000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11255000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9866000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10910000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9927000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10082000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12123000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12059000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8866000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11943000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11389000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>14284000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11052000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>12080000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12346000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10229000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>8947000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>9877000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>11114000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>8942000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>9218000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>10142000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>10995000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5700000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4877000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6781000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4887000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4897000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4277000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6843000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5302000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4360000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3758000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4601000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4647000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4270000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4335000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4229000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5921000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4908000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4568000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3494000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4470000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3548000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4033000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2392000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3911000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4434000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4938000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3752000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5141000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5421000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5121000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4063000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5736000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5002000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5957000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4891000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-5006000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-4966000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-11568000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-6233000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-5581000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5941000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11655000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4344000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6086000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4958000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5363000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5150000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4016000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2961000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5874000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4545000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5423000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3818000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3823000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5543000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3788000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12651000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4756000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3298000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3779000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26852000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>178000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3448000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5256000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5022000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3688000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5703000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1898000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5401000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3158000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7352000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-45483000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7152000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4579000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4967000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3428000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5969000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-6026000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-8172000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,29 +10471,29 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2014000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2010000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2086000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-3749000</v>
       </c>
       <c r="U96" s="3">
         <v>-3749000</v>
       </c>
       <c r="V96" s="3">
+        <v>-3749000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-3748000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3830000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-3741000</v>
       </c>
       <c r="Y96" s="3">
         <v>-3741000</v>
@@ -10269,55 +10502,58 @@
         <v>-3741000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-3737000</v>
+        <v>-3741000</v>
       </c>
       <c r="AB96" s="3">
         <v>-3737000</v>
       </c>
       <c r="AC96" s="3">
-        <v>-3726000</v>
+        <v>-3737000</v>
       </c>
       <c r="AD96" s="3">
         <v>-3726000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-3726000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3722000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3714000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-3635000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-3631000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-3074000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-3070000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-3008000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-3009000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-3009000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-2947000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-2951000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8777000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2989000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-553000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5853000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5562000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5478000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7815000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6330000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7754000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2181000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3711000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5191000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6151000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36650000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>24251000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6587000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3735000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6583000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>18483000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-10239000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15857000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>188000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6099000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2742000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7558000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-10362000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4421000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-12310000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9959000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-218000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3502000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2773000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>17086000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>5568000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>6049000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-4223000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-4136000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5609000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6195000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1801000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9752000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3632000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3538000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>680000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-477000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-401000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3229000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-826000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1963000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6680000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-851000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1299000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1623000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-34531000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17332000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-89000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9429000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>548000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1558000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>21000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7182000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6991000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2255000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5513000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1872000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2024000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1230000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3388000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4965000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-35472000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1707000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2186000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22921000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>10794000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>9096000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-107000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1313000</v>
       </c>
     </row>
